--- a/data/final/series/bcb_sgs_var_pct_ibc_br.xlsx
+++ b/data/final/series/bcb_sgs_var_pct_ibc_br.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,7 +437,7 @@
         <v>44500</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.59426</v>
+        <v>-0.594556</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         <v>44530</v>
       </c>
       <c r="B3" t="n">
-        <v>1.373375</v>
+        <v>1.36989</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         <v>44561</v>
       </c>
       <c r="B4" t="n">
-        <v>1.500312</v>
+        <v>1.502063</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>44592</v>
       </c>
       <c r="B5" t="n">
-        <v>-7.700102</v>
+        <v>-7.696961</v>
       </c>
     </row>
     <row r="6">
@@ -469,7 +469,7 @@
         <v>44620</v>
       </c>
       <c r="B6" t="n">
-        <v>4.326098</v>
+        <v>4.318965</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>44651</v>
       </c>
       <c r="B7" t="n">
-        <v>9.297102000000001</v>
+        <v>9.300848999999999</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v>44681</v>
       </c>
       <c r="B8" t="n">
-        <v>-4.120958</v>
+        <v>-4.116419</v>
       </c>
     </row>
     <row r="9">
@@ -493,7 +493,7 @@
         <v>44712</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.477049</v>
+        <v>-0.484439</v>
       </c>
     </row>
     <row r="10">
@@ -501,7 +501,7 @@
         <v>44742</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.426943</v>
+        <v>-0.428397</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>44773</v>
       </c>
       <c r="B11" t="n">
-        <v>4.665299</v>
+        <v>4.675335</v>
       </c>
     </row>
     <row r="12">
@@ -517,7 +517,7 @@
         <v>44804</v>
       </c>
       <c r="B12" t="n">
-        <v>0.538824</v>
+        <v>0.530637</v>
       </c>
     </row>
     <row r="13">
@@ -525,7 +525,7 @@
         <v>44834</v>
       </c>
       <c r="B13" t="n">
-        <v>-3.179174</v>
+        <v>-3.179227</v>
       </c>
     </row>
     <row r="14">
@@ -533,7 +533,7 @@
         <v>44865</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.103679</v>
+        <v>-1.094122</v>
       </c>
     </row>
     <row r="15">
@@ -541,7 +541,7 @@
         <v>44895</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.920772</v>
+        <v>-0.930689</v>
       </c>
     </row>
     <row r="16">
@@ -549,7 +549,7 @@
         <v>44926</v>
       </c>
       <c r="B16" t="n">
-        <v>0.827113</v>
+        <v>0.827078</v>
       </c>
     </row>
     <row r="17">
@@ -557,7 +557,7 @@
         <v>44957</v>
       </c>
       <c r="B17" t="n">
-        <v>-4.880959</v>
+        <v>-4.872284</v>
       </c>
     </row>
     <row r="18">
@@ -565,7 +565,7 @@
         <v>44985</v>
       </c>
       <c r="B18" t="n">
-        <v>3.73991</v>
+        <v>3.731301</v>
       </c>
     </row>
     <row r="19">
@@ -573,7 +573,7 @@
         <v>45016</v>
       </c>
       <c r="B19" t="n">
-        <v>12.134092</v>
+        <v>12.135312</v>
       </c>
     </row>
     <row r="20">
@@ -581,7 +581,7 @@
         <v>45046</v>
       </c>
       <c r="B20" t="n">
-        <v>-5.952841</v>
+        <v>-5.946769</v>
       </c>
     </row>
     <row r="21">
@@ -589,7 +589,7 @@
         <v>45077</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.267588</v>
+        <v>-1.275652</v>
       </c>
     </row>
     <row r="22">
@@ -597,7 +597,7 @@
         <v>45107</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.420234</v>
+        <v>-0.418863</v>
       </c>
     </row>
     <row r="23">
@@ -605,7 +605,7 @@
         <v>45138</v>
       </c>
       <c r="B23" t="n">
-        <v>2.985912</v>
+        <v>2.992877</v>
       </c>
     </row>
     <row r="24">
@@ -613,7 +613,7 @@
         <v>45169</v>
       </c>
       <c r="B24" t="n">
-        <v>0.683801</v>
+        <v>0.676</v>
       </c>
     </row>
     <row r="25">
@@ -621,7 +621,7 @@
         <v>45199</v>
       </c>
       <c r="B25" t="n">
-        <v>-4.05153</v>
+        <v>-4.052448</v>
       </c>
     </row>
     <row r="26">
@@ -629,7 +629,7 @@
         <v>45230</v>
       </c>
       <c r="B26" t="n">
-        <v>0.163194</v>
+        <v>0.171808</v>
       </c>
     </row>
     <row r="27">
@@ -637,7 +637,7 @@
         <v>45260</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.241748</v>
+        <v>-0.248573</v>
       </c>
     </row>
     <row r="28">
@@ -645,7 +645,7 @@
         <v>45291</v>
       </c>
       <c r="B28" t="n">
-        <v>0.004367</v>
+        <v>0.004199</v>
       </c>
     </row>
     <row r="29">
@@ -653,7 +653,7 @@
         <v>45322</v>
       </c>
       <c r="B29" t="n">
-        <v>-2.355435</v>
+        <v>-2.347954</v>
       </c>
     </row>
     <row r="30">
@@ -661,7 +661,7 @@
         <v>45351</v>
       </c>
       <c r="B30" t="n">
-        <v>2.880633</v>
+        <v>2.873375</v>
       </c>
     </row>
     <row r="31">
@@ -669,7 +669,7 @@
         <v>45382</v>
       </c>
       <c r="B31" t="n">
-        <v>7.264557</v>
+        <v>7.262481</v>
       </c>
     </row>
     <row r="32">
@@ -677,7 +677,7 @@
         <v>45412</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.292209</v>
+        <v>-0.284579</v>
       </c>
     </row>
     <row r="33">
@@ -685,7 +685,7 @@
         <v>45443</v>
       </c>
       <c r="B33" t="n">
-        <v>-4.155585</v>
+        <v>-4.159973</v>
       </c>
     </row>
     <row r="34">
@@ -693,7 +693,7 @@
         <v>45473</v>
       </c>
       <c r="B34" t="n">
-        <v>1.108973</v>
+        <v>1.104953</v>
       </c>
     </row>
     <row r="35">
@@ -701,7 +701,7 @@
         <v>45504</v>
       </c>
       <c r="B35" t="n">
-        <v>5.318521</v>
+        <v>5.327189</v>
       </c>
     </row>
     <row r="36">
@@ -709,7 +709,7 @@
         <v>45535</v>
       </c>
       <c r="B36" t="n">
-        <v>-1.292936</v>
+        <v>-1.297169</v>
       </c>
     </row>
     <row r="37">
@@ -717,7 +717,7 @@
         <v>45565</v>
       </c>
       <c r="B37" t="n">
-        <v>-2.707476</v>
+        <v>-2.711204</v>
       </c>
     </row>
     <row r="38">
@@ -725,7 +725,7 @@
         <v>45596</v>
       </c>
       <c r="B38" t="n">
-        <v>1.957468</v>
+        <v>1.966099</v>
       </c>
     </row>
     <row r="39">
@@ -733,7 +733,7 @@
         <v>45626</v>
       </c>
       <c r="B39" t="n">
-        <v>-3.378769</v>
+        <v>-3.383039</v>
       </c>
     </row>
     <row r="40">
@@ -741,7 +741,7 @@
         <v>45657</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.263097</v>
+        <v>-1.265086</v>
       </c>
     </row>
     <row r="41">
@@ -749,7 +749,7 @@
         <v>45688</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.472655</v>
+        <v>-1.465146</v>
       </c>
     </row>
     <row r="42">
@@ -757,7 +757,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>4.09588</v>
+        <v>4.088981</v>
       </c>
     </row>
     <row r="43">
@@ -765,7 +765,7 @@
         <v>45747</v>
       </c>
       <c r="B43" t="n">
-        <v>6.739292</v>
+        <v>6.734953</v>
       </c>
     </row>
     <row r="44">
@@ -773,7 +773,7 @@
         <v>45777</v>
       </c>
       <c r="B44" t="n">
-        <v>-1.260911</v>
+        <v>-1.250256</v>
       </c>
     </row>
     <row r="45">
@@ -781,7 +781,7 @@
         <v>45808</v>
       </c>
       <c r="B45" t="n">
-        <v>-3.581128</v>
+        <v>-3.586372</v>
       </c>
     </row>
     <row r="46">
@@ -789,7 +789,7 @@
         <v>45838</v>
       </c>
       <c r="B46" t="n">
-        <v>-1.094212</v>
+        <v>-1.100666</v>
       </c>
     </row>
     <row r="47">
@@ -797,7 +797,7 @@
         <v>45869</v>
       </c>
       <c r="B47" t="n">
-        <v>5.341227</v>
+        <v>5.352993</v>
       </c>
     </row>
     <row r="48">
@@ -805,7 +805,7 @@
         <v>45900</v>
       </c>
       <c r="B48" t="n">
-        <v>-2.407934</v>
+        <v>-2.412481</v>
       </c>
     </row>
     <row r="49">
@@ -813,7 +813,7 @@
         <v>45930</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.807491</v>
+        <v>-0.812453</v>
       </c>
     </row>
     <row r="50">
@@ -821,7 +821,7 @@
         <v>45961</v>
       </c>
       <c r="B50" t="n">
-        <v>0.525396</v>
+        <v>0.541697</v>
       </c>
     </row>
     <row r="51">
@@ -829,7 +829,7 @@
         <v>45991</v>
       </c>
       <c r="B51" t="n">
-        <v>-3.151492</v>
+        <v>-3.159521</v>
       </c>
     </row>
     <row r="52">
@@ -837,7 +837,7 @@
         <v>46022</v>
       </c>
       <c r="B52" t="n">
-        <v>0.560793</v>
+        <v>0.549021</v>
       </c>
     </row>
     <row r="53">
@@ -845,7 +845,7 @@
         <v>46053</v>
       </c>
       <c r="B53" t="n">
-        <v>-3.182366</v>
+        <v>-3.178231</v>
       </c>
     </row>
     <row r="54">
@@ -853,7 +853,7 @@
         <v>46081</v>
       </c>
       <c r="B54" t="n">
-        <v>2.880001</v>
+        <v>2.874551</v>
       </c>
     </row>
     <row r="55">
@@ -861,7 +861,7 @@
         <v>46112</v>
       </c>
       <c r="B55" t="n">
-        <v>10.517667</v>
+        <v>10.543613</v>
       </c>
     </row>
     <row r="56">
@@ -869,7 +869,7 @@
         <v>46142</v>
       </c>
       <c r="B56" t="n">
-        <v>-3.475583</v>
+        <v>-3.409876</v>
       </c>
     </row>
     <row r="57">
@@ -877,7 +877,7 @@
         <v>46173</v>
       </c>
       <c r="B57" t="n">
-        <v>-3.836192</v>
+        <v>-3.805639</v>
       </c>
     </row>
     <row r="58">
@@ -885,7 +885,15 @@
         <v>46203</v>
       </c>
       <c r="B58" t="n">
-        <v>0.332557</v>
+        <v>0.261521</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4.057001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/series/bcb_sgs_var_pct_ibc_br.xlsx
+++ b/data/final/series/bcb_sgs_var_pct_ibc_br.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,465 +434,457 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.594556</v>
+        <v>1.36989</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B3" t="n">
-        <v>1.36989</v>
+        <v>1.502063</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B4" t="n">
-        <v>1.502063</v>
+        <v>-7.696961</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B5" t="n">
-        <v>-7.696961</v>
+        <v>4.318965</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B6" t="n">
-        <v>4.318965</v>
+        <v>9.300848999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B7" t="n">
-        <v>9.300848999999999</v>
+        <v>-4.116419</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B8" t="n">
-        <v>-4.116419</v>
+        <v>-0.484439</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.484439</v>
+        <v>-0.428397</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.428397</v>
+        <v>4.675335</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B11" t="n">
-        <v>4.675335</v>
+        <v>0.530637</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B12" t="n">
-        <v>0.530637</v>
+        <v>-3.179227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B13" t="n">
-        <v>-3.179227</v>
+        <v>-1.094122</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.094122</v>
+        <v>-0.930689</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.930689</v>
+        <v>0.827078</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B16" t="n">
-        <v>0.827078</v>
+        <v>-4.872284</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B17" t="n">
-        <v>-4.872284</v>
+        <v>3.731301</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B18" t="n">
-        <v>3.731301</v>
+        <v>12.135312</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B19" t="n">
-        <v>12.135312</v>
+        <v>-5.946769</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B20" t="n">
-        <v>-5.946769</v>
+        <v>-1.275652</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.275652</v>
+        <v>-0.418863</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.418863</v>
+        <v>2.992877</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B23" t="n">
-        <v>2.992877</v>
+        <v>0.676</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B24" t="n">
-        <v>0.676</v>
+        <v>-4.052448</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B25" t="n">
-        <v>-4.052448</v>
+        <v>0.171808</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B26" t="n">
-        <v>0.171808</v>
+        <v>-0.248573</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.248573</v>
+        <v>0.004199</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B28" t="n">
-        <v>0.004199</v>
+        <v>-2.347954</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B29" t="n">
-        <v>-2.347954</v>
+        <v>2.873375</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B30" t="n">
-        <v>2.873375</v>
+        <v>7.262481</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B31" t="n">
-        <v>7.262481</v>
+        <v>-0.284579</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.284579</v>
+        <v>-4.159973</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B33" t="n">
-        <v>-4.159973</v>
+        <v>1.104953</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B34" t="n">
-        <v>1.104953</v>
+        <v>5.327189</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B35" t="n">
-        <v>5.327189</v>
+        <v>-1.297169</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B36" t="n">
-        <v>-1.297169</v>
+        <v>-2.711204</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B37" t="n">
-        <v>-2.711204</v>
+        <v>1.966099</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B38" t="n">
-        <v>1.966099</v>
+        <v>-3.383039</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B39" t="n">
-        <v>-3.383039</v>
+        <v>-1.265086</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.265086</v>
+        <v>-1.465146</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.465146</v>
+        <v>4.088981</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B42" t="n">
-        <v>4.088981</v>
+        <v>6.734953</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B43" t="n">
-        <v>6.734953</v>
+        <v>-1.250256</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B44" t="n">
-        <v>-1.250256</v>
+        <v>-3.586372</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B45" t="n">
-        <v>-3.586372</v>
+        <v>-1.100666</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B46" t="n">
-        <v>-1.100666</v>
+        <v>5.352993</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B47" t="n">
-        <v>5.352993</v>
+        <v>-2.412481</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B48" t="n">
-        <v>-2.412481</v>
+        <v>-0.812453</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.812453</v>
+        <v>0.541697</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B50" t="n">
-        <v>0.541697</v>
+        <v>-3.159521</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B51" t="n">
-        <v>-3.159521</v>
+        <v>0.549021</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B52" t="n">
-        <v>0.549021</v>
+        <v>-3.178231</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B53" t="n">
-        <v>-3.178231</v>
+        <v>2.874551</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B54" t="n">
-        <v>2.874551</v>
+        <v>10.543613</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B55" t="n">
-        <v>10.543613</v>
+        <v>-3.409876</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B56" t="n">
-        <v>-3.409876</v>
+        <v>-3.805639</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B57" t="n">
-        <v>-3.805639</v>
+        <v>0.261521</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B58" t="n">
-        <v>0.261521</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="B59" t="n">
         <v>4.057001</v>
       </c>
     </row>

--- a/data/final/series/bcb_sgs_var_pct_ibc_br.xlsx
+++ b/data/final/series/bcb_sgs_var_pct_ibc_br.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,7 +437,7 @@
         <v>44530</v>
       </c>
       <c r="B2" t="n">
-        <v>1.36989</v>
+        <v>1.362679</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         <v>44561</v>
       </c>
       <c r="B3" t="n">
-        <v>1.502063</v>
+        <v>1.499555</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +453,7 @@
         <v>44592</v>
       </c>
       <c r="B4" t="n">
-        <v>-7.696961</v>
+        <v>-7.689646</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>44620</v>
       </c>
       <c r="B5" t="n">
-        <v>4.318965</v>
+        <v>4.321555</v>
       </c>
     </row>
     <row r="6">
@@ -469,7 +469,7 @@
         <v>44651</v>
       </c>
       <c r="B6" t="n">
-        <v>9.300848999999999</v>
+        <v>9.303654</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>44681</v>
       </c>
       <c r="B7" t="n">
-        <v>-4.116419</v>
+        <v>-4.109192</v>
       </c>
     </row>
     <row r="8">
@@ -485,7 +485,7 @@
         <v>44712</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.484439</v>
+        <v>-0.503762</v>
       </c>
     </row>
     <row r="9">
@@ -493,7 +493,7 @@
         <v>44742</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.428397</v>
+        <v>-0.432762</v>
       </c>
     </row>
     <row r="10">
@@ -501,7 +501,7 @@
         <v>44773</v>
       </c>
       <c r="B10" t="n">
-        <v>4.675335</v>
+        <v>4.684327</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>44804</v>
       </c>
       <c r="B11" t="n">
-        <v>0.530637</v>
+        <v>0.525053</v>
       </c>
     </row>
     <row r="12">
@@ -517,7 +517,7 @@
         <v>44834</v>
       </c>
       <c r="B12" t="n">
-        <v>-3.179227</v>
+        <v>-3.184433</v>
       </c>
     </row>
     <row r="13">
@@ -525,7 +525,7 @@
         <v>44865</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.094122</v>
+        <v>-1.083358</v>
       </c>
     </row>
     <row r="14">
@@ -533,7 +533,7 @@
         <v>44895</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.930689</v>
+        <v>-0.934407</v>
       </c>
     </row>
     <row r="15">
@@ -541,7 +541,7 @@
         <v>44926</v>
       </c>
       <c r="B15" t="n">
-        <v>0.827078</v>
+        <v>0.82123</v>
       </c>
     </row>
     <row r="16">
@@ -549,7 +549,7 @@
         <v>44957</v>
       </c>
       <c r="B16" t="n">
-        <v>-4.872284</v>
+        <v>-4.859596</v>
       </c>
     </row>
     <row r="17">
@@ -557,7 +557,7 @@
         <v>44985</v>
       </c>
       <c r="B17" t="n">
-        <v>3.731301</v>
+        <v>3.72657</v>
       </c>
     </row>
     <row r="18">
@@ -565,7 +565,7 @@
         <v>45016</v>
       </c>
       <c r="B18" t="n">
-        <v>12.135312</v>
+        <v>12.13037</v>
       </c>
     </row>
     <row r="19">
@@ -573,7 +573,7 @@
         <v>45046</v>
       </c>
       <c r="B19" t="n">
-        <v>-5.946769</v>
+        <v>-5.938874</v>
       </c>
     </row>
     <row r="20">
@@ -581,7 +581,7 @@
         <v>45077</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.275652</v>
+        <v>-1.27926</v>
       </c>
     </row>
     <row r="21">
@@ -589,7 +589,7 @@
         <v>45107</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.418863</v>
+        <v>-0.42403</v>
       </c>
     </row>
     <row r="22">
@@ -597,7 +597,7 @@
         <v>45138</v>
       </c>
       <c r="B22" t="n">
-        <v>2.992877</v>
+        <v>3.002607</v>
       </c>
     </row>
     <row r="23">
@@ -605,7 +605,7 @@
         <v>45169</v>
       </c>
       <c r="B23" t="n">
-        <v>0.676</v>
+        <v>0.670651</v>
       </c>
     </row>
     <row r="24">
@@ -613,7 +613,7 @@
         <v>45199</v>
       </c>
       <c r="B24" t="n">
-        <v>-4.052448</v>
+        <v>-4.056344</v>
       </c>
     </row>
     <row r="25">
@@ -621,7 +621,7 @@
         <v>45230</v>
       </c>
       <c r="B25" t="n">
-        <v>0.171808</v>
+        <v>0.182813</v>
       </c>
     </row>
     <row r="26">
@@ -629,7 +629,7 @@
         <v>45260</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.248573</v>
+        <v>-0.2556</v>
       </c>
     </row>
     <row r="27">
@@ -637,7 +637,7 @@
         <v>45291</v>
       </c>
       <c r="B27" t="n">
-        <v>0.004199</v>
+        <v>-0.001967</v>
       </c>
     </row>
     <row r="28">
@@ -645,7 +645,7 @@
         <v>45322</v>
       </c>
       <c r="B28" t="n">
-        <v>-2.347954</v>
+        <v>-2.334286</v>
       </c>
     </row>
     <row r="29">
@@ -653,7 +653,7 @@
         <v>45351</v>
       </c>
       <c r="B29" t="n">
-        <v>2.873375</v>
+        <v>2.868707</v>
       </c>
     </row>
     <row r="30">
@@ -661,7 +661,7 @@
         <v>45382</v>
       </c>
       <c r="B30" t="n">
-        <v>7.262481</v>
+        <v>7.253134</v>
       </c>
     </row>
     <row r="31">
@@ -669,7 +669,7 @@
         <v>45412</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.284579</v>
+        <v>-0.273497</v>
       </c>
     </row>
     <row r="32">
@@ -677,7 +677,7 @@
         <v>45443</v>
       </c>
       <c r="B32" t="n">
-        <v>-4.159973</v>
+        <v>-4.167661</v>
       </c>
     </row>
     <row r="33">
@@ -685,7 +685,7 @@
         <v>45473</v>
       </c>
       <c r="B33" t="n">
-        <v>1.104953</v>
+        <v>1.102474</v>
       </c>
     </row>
     <row r="34">
@@ -693,7 +693,7 @@
         <v>45504</v>
       </c>
       <c r="B34" t="n">
-        <v>5.327189</v>
+        <v>5.339918</v>
       </c>
     </row>
     <row r="35">
@@ -701,7 +701,7 @@
         <v>45535</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.297169</v>
+        <v>-1.301593</v>
       </c>
     </row>
     <row r="36">
@@ -709,7 +709,7 @@
         <v>45565</v>
       </c>
       <c r="B36" t="n">
-        <v>-2.711204</v>
+        <v>-2.715842</v>
       </c>
     </row>
     <row r="37">
@@ -717,7 +717,7 @@
         <v>45596</v>
       </c>
       <c r="B37" t="n">
-        <v>1.966099</v>
+        <v>1.97732</v>
       </c>
     </row>
     <row r="38">
@@ -725,7 +725,7 @@
         <v>45626</v>
       </c>
       <c r="B38" t="n">
-        <v>-3.383039</v>
+        <v>-3.387772</v>
       </c>
     </row>
     <row r="39">
@@ -733,7 +733,7 @@
         <v>45657</v>
       </c>
       <c r="B39" t="n">
-        <v>-1.265086</v>
+        <v>-1.273108</v>
       </c>
     </row>
     <row r="40">
@@ -741,7 +741,7 @@
         <v>45688</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.465146</v>
+        <v>-1.466941</v>
       </c>
     </row>
     <row r="41">
@@ -749,7 +749,7 @@
         <v>45716</v>
       </c>
       <c r="B41" t="n">
-        <v>4.088981</v>
+        <v>4.061062</v>
       </c>
     </row>
     <row r="42">
@@ -757,7 +757,7 @@
         <v>45747</v>
       </c>
       <c r="B42" t="n">
-        <v>6.734953</v>
+        <v>6.746107</v>
       </c>
     </row>
     <row r="43">
@@ -765,7 +765,7 @@
         <v>45777</v>
       </c>
       <c r="B43" t="n">
-        <v>-1.250256</v>
+        <v>-1.222443</v>
       </c>
     </row>
     <row r="44">
@@ -773,7 +773,7 @@
         <v>45808</v>
       </c>
       <c r="B44" t="n">
-        <v>-3.586372</v>
+        <v>-3.56912</v>
       </c>
     </row>
     <row r="45">
@@ -781,7 +781,7 @@
         <v>45838</v>
       </c>
       <c r="B45" t="n">
-        <v>-1.100666</v>
+        <v>-1.084136</v>
       </c>
     </row>
     <row r="46">
@@ -789,7 +789,7 @@
         <v>45869</v>
       </c>
       <c r="B46" t="n">
-        <v>5.352993</v>
+        <v>5.395553</v>
       </c>
     </row>
     <row r="47">
@@ -797,7 +797,7 @@
         <v>45900</v>
       </c>
       <c r="B47" t="n">
-        <v>-2.412481</v>
+        <v>-2.4886</v>
       </c>
     </row>
     <row r="48">
@@ -805,7 +805,7 @@
         <v>45930</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.812453</v>
+        <v>-0.83934</v>
       </c>
     </row>
     <row r="49">
@@ -813,7 +813,7 @@
         <v>45961</v>
       </c>
       <c r="B49" t="n">
-        <v>0.541697</v>
+        <v>0.534678</v>
       </c>
     </row>
     <row r="50">
@@ -821,7 +821,7 @@
         <v>45991</v>
       </c>
       <c r="B50" t="n">
-        <v>-3.159521</v>
+        <v>-3.147402</v>
       </c>
     </row>
     <row r="51">
@@ -829,7 +829,7 @@
         <v>46022</v>
       </c>
       <c r="B51" t="n">
-        <v>0.549021</v>
+        <v>0.574704</v>
       </c>
     </row>
     <row r="52">
@@ -837,7 +837,7 @@
         <v>46053</v>
       </c>
       <c r="B52" t="n">
-        <v>-3.178231</v>
+        <v>-3.053897</v>
       </c>
     </row>
     <row r="53">
@@ -845,7 +845,7 @@
         <v>46081</v>
       </c>
       <c r="B53" t="n">
-        <v>2.874551</v>
+        <v>2.832634</v>
       </c>
     </row>
     <row r="54">
@@ -853,7 +853,7 @@
         <v>46112</v>
       </c>
       <c r="B54" t="n">
-        <v>10.543613</v>
+        <v>10.485752</v>
       </c>
     </row>
     <row r="55">
@@ -861,7 +861,7 @@
         <v>46142</v>
       </c>
       <c r="B55" t="n">
-        <v>-3.409876</v>
+        <v>-3.309152</v>
       </c>
     </row>
     <row r="56">
@@ -869,7 +869,7 @@
         <v>46173</v>
       </c>
       <c r="B56" t="n">
-        <v>-3.805639</v>
+        <v>-3.823187</v>
       </c>
     </row>
     <row r="57">
@@ -877,7 +877,7 @@
         <v>46203</v>
       </c>
       <c r="B57" t="n">
-        <v>0.261521</v>
+        <v>0.355099</v>
       </c>
     </row>
     <row r="58">
@@ -885,7 +885,15 @@
         <v>46234</v>
       </c>
       <c r="B58" t="n">
-        <v>4.057001</v>
+        <v>3.907408</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B59" t="n">
+        <v>-2.420065</v>
       </c>
     </row>
   </sheetData>
